--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -56,7 +56,7 @@
     <t>副本杀怪</t>
   </si>
   <si>
-    <t>等级</t>
+    <t>角色</t>
   </si>
   <si>
     <t>技能</t>
@@ -1282,7 +1282,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>_id</t>
   </si>
@@ -56,6 +56,9 @@
     <t>副本杀怪</t>
   </si>
   <si>
+    <t>玩法养成</t>
+  </si>
+  <si>
     <t>角色</t>
   </si>
   <si>
@@ -93,6 +96,9 @@
   </si>
   <si>
     <t>区域杀手</t>
+  </si>
+  <si>
+    <t>守卫龙城</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E27"/>
+  <dimension ref="C3:E30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1132,7 +1138,15 @@
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:5">
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:5">
       <c r="C10" s="3"/>
@@ -1142,7 +1156,7 @@
         <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
@@ -1153,7 +1167,7 @@
         <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
@@ -1164,7 +1178,7 @@
         <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -1175,7 +1189,7 @@
         <v>201</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="3">
         <v>2</v>
@@ -1186,7 +1200,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3">
         <v>2</v>
@@ -1197,7 +1211,7 @@
         <v>203</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
@@ -1208,7 +1222,7 @@
         <v>301</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="3">
         <v>3</v>
@@ -1219,7 +1233,7 @@
         <v>302</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="3">
         <v>3</v>
@@ -1230,7 +1244,7 @@
         <v>303</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23" s="3">
         <v>3</v>
@@ -1241,7 +1255,7 @@
         <v>304</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="3">
         <v>3</v>
@@ -1252,7 +1266,7 @@
         <v>305</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="3">
         <v>3</v>
@@ -1263,7 +1277,7 @@
         <v>306</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="3">
         <v>3</v>
@@ -1274,10 +1288,21 @@
         <v>307</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:5">
+      <c r="C30" s="3">
+        <v>401</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>_id</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>装备强化</t>
+  </si>
+  <si>
+    <t>传世强化</t>
   </si>
   <si>
     <t>通关副本</t>
@@ -1063,7 +1066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E30"/>
+  <dimension ref="C3:E31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1217,20 +1220,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:5">
-      <c r="C21" s="3">
-        <v>301</v>
-      </c>
-      <c r="D21" s="3" t="s">
+    <row r="20" customHeight="1" spans="3:5">
+      <c r="C20" s="3">
+        <v>204</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="3">
-        <v>3</v>
+      <c r="E20" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:5">
       <c r="C22" s="3">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>17</v>
@@ -1241,7 +1244,7 @@
     </row>
     <row r="23" customHeight="1" spans="3:5">
       <c r="C23" s="3">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>18</v>
@@ -1252,7 +1255,7 @@
     </row>
     <row r="24" customHeight="1" spans="3:5">
       <c r="C24" s="3">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>19</v>
@@ -1263,7 +1266,7 @@
     </row>
     <row r="25" customHeight="1" spans="3:5">
       <c r="C25" s="3">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>20</v>
@@ -1274,7 +1277,7 @@
     </row>
     <row r="26" customHeight="1" spans="3:5">
       <c r="C26" s="3">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>21</v>
@@ -1285,7 +1288,7 @@
     </row>
     <row r="27" customHeight="1" spans="3:5">
       <c r="C27" s="3">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>22</v>
@@ -1294,14 +1297,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:5">
-      <c r="C30" s="3">
+    <row r="28" customHeight="1" spans="3:5">
+      <c r="C28" s="3">
+        <v>307</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:5">
+      <c r="C31" s="3">
         <v>401</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="3">
         <v>4</v>
       </c>
     </row>

--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>_id</t>
   </si>
@@ -59,6 +59,9 @@
     <t>玩法养成</t>
   </si>
   <si>
+    <t>神秘彩蛋</t>
+  </si>
+  <si>
     <t>角色</t>
   </si>
   <si>
@@ -102,6 +105,12 @@
   </si>
   <si>
     <t>守卫龙城</t>
+  </si>
+  <si>
+    <t>彩蛋成就</t>
+  </si>
+  <si>
+    <t>神秘成就</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E31"/>
+  <dimension ref="C3:E34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1152,14 +1161,22 @@
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:5">
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customHeight="1" spans="3:5">
       <c r="C12" s="3">
         <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
@@ -1170,7 +1187,7 @@
         <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
@@ -1181,7 +1198,7 @@
         <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -1192,7 +1209,7 @@
         <v>201</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="3">
         <v>2</v>
@@ -1203,7 +1220,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="3">
         <v>2</v>
@@ -1214,7 +1231,7 @@
         <v>203</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
@@ -1225,7 +1242,7 @@
         <v>204</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3">
         <v>2</v>
@@ -1236,7 +1253,7 @@
         <v>301</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" s="3">
         <v>3</v>
@@ -1247,7 +1264,7 @@
         <v>302</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="3">
         <v>3</v>
@@ -1258,7 +1275,7 @@
         <v>303</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" s="3">
         <v>3</v>
@@ -1269,7 +1286,7 @@
         <v>304</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="3">
         <v>3</v>
@@ -1280,7 +1297,7 @@
         <v>305</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="3">
         <v>3</v>
@@ -1291,7 +1308,7 @@
         <v>306</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" s="3">
         <v>3</v>
@@ -1302,7 +1319,7 @@
         <v>307</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3">
         <v>3</v>
@@ -1313,10 +1330,32 @@
         <v>401</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>4</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:5">
+      <c r="C33" s="3">
+        <v>501</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:5">
+      <c r="C34" s="3">
+        <v>502</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -71,7 +71,7 @@
     <t>宠物</t>
   </si>
   <si>
-    <t>装备穿戴</t>
+    <t>装备获取</t>
   </si>
   <si>
     <t>装备精炼</t>

--- a/Excel/AchievementGroupConfig.xlsx
+++ b/Excel/AchievementGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>_id</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>传世强化</t>
+  </si>
+  <si>
+    <t>四格进阶</t>
   </si>
   <si>
     <t>通关副本</t>
@@ -1075,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E34"/>
+  <dimension ref="C3:E35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1248,20 +1251,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:5">
-      <c r="C22" s="3">
-        <v>301</v>
-      </c>
-      <c r="D22" s="3" t="s">
+    <row r="21" customHeight="1" spans="3:5">
+      <c r="C21" s="3">
+        <v>205</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="3">
-        <v>3</v>
+      <c r="E21" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:5">
       <c r="C23" s="3">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>19</v>
@@ -1272,7 +1275,7 @@
     </row>
     <row r="24" customHeight="1" spans="3:5">
       <c r="C24" s="3">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>20</v>
@@ -1283,7 +1286,7 @@
     </row>
     <row r="25" customHeight="1" spans="3:5">
       <c r="C25" s="3">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>21</v>
@@ -1294,7 +1297,7 @@
     </row>
     <row r="26" customHeight="1" spans="3:5">
       <c r="C26" s="3">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>22</v>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="27" customHeight="1" spans="3:5">
       <c r="C27" s="3">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>23</v>
@@ -1316,7 +1319,7 @@
     </row>
     <row r="28" customHeight="1" spans="3:5">
       <c r="C28" s="3">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>24</v>
@@ -1325,36 +1328,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:5">
-      <c r="C31" s="3">
+    <row r="29" customHeight="1" spans="3:5">
+      <c r="C29" s="3">
+        <v>307</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:5">
+      <c r="C32" s="3">
         <v>401</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:5">
-      <c r="C33" s="3">
-        <v>501</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>5</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:5">
       <c r="C34" s="3">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:5">
+      <c r="C35" s="3">
+        <v>502</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="3">
         <v>5</v>
       </c>
     </row>
